--- a/sources/julia_step4.xlsx
+++ b/sources/julia_step4.xlsx
@@ -423,8 +423,8 @@
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">

--- a/sources/julia_step4.xlsx
+++ b/sources/julia_step4.xlsx
@@ -822,6 +822,11 @@
           <t>Special Tag Throw with Michelle only. Michelle finishes with a Lariat. Total damage is 12,24.</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
@@ -864,6 +869,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
@@ -906,6 +916,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
@@ -946,6 +961,11 @@
       <c r="L12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -5441,6 +5461,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
@@ -5468,6 +5493,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
@@ -5493,6 +5523,11 @@
       <c r="J105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">

--- a/sources/julia_step4.xlsx
+++ b/sources/julia_step4.xlsx
@@ -3812,6 +3812,11 @@
           <t>– 1+2</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>– Back Push</t>
